--- a/multi seed generators/merged 10 seeds/classification/results/aggregated/utility_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/classification/results/aggregated/utility_mean_sd.xlsx
@@ -334,11 +334,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -547,11 +547,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
@@ -760,11 +760,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -973,11 +973,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R12" s="2" t="n">
@@ -1186,11 +1186,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -1399,11 +1399,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R18" s="2" t="n">
@@ -1612,11 +1612,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -1825,11 +1825,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R24" s="2" t="n">
@@ -2038,11 +2038,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P27" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -2251,11 +2251,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R30" s="2" t="n">
@@ -2464,11 +2464,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -2677,11 +2677,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R36" s="2" t="n">
@@ -2890,11 +2890,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P39" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3103,11 +3103,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R42" s="2" t="n">
@@ -3316,11 +3316,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -3529,11 +3529,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P48" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R48" s="2" t="n">
@@ -3742,11 +3742,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R51" t="n">
@@ -3955,11 +3955,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P54" s="2" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R54" s="2" t="n">
@@ -4168,11 +4168,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P57" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -4381,11 +4381,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P60" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R60" s="2" t="n">
@@ -4523,11 +4523,11 @@
         <v>0.1058333333333334</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>0.0</v>
+        <v>0.1161233242582282</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.105833 ± 0</t>
+          <t xml:space="preserve">0.105833 ± 0.116123</t>
         </is>
       </c>
       <c r="R62" s="2" t="n">
@@ -4594,11 +4594,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P63" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -4665,11 +4665,11 @@
         <v>0.715</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>0.0</v>
+        <v>0.11085094061162838</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715 ± 0</t>
+          <t xml:space="preserve">0.715 ± 0.110851</t>
         </is>
       </c>
       <c r="R64" s="2" t="n">
@@ -4736,11 +4736,11 @@
         <v>0.1291971996159116</v>
       </c>
       <c r="P65" t="n">
-        <v>0.0</v>
+        <v>0.08377018626254526</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.129197 ± 0</t>
+          <t xml:space="preserve">0.129197 ± 0.0837702</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -4807,11 +4807,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R66" s="2" t="n">
@@ -4878,11 +4878,11 @@
         <v>0.6885921785323337</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0</v>
+        <v>0.0791458413088965</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.688592 ± 0</t>
+          <t xml:space="preserve">0.688592 ± 0.0791458</t>
         </is>
       </c>
       <c r="R67" t="n">
@@ -4949,11 +4949,11 @@
         <v>0.1159762049533802</v>
       </c>
       <c r="P68" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07702492203327668</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.115976 ± 0</t>
+          <t xml:space="preserve">0.115976 ± 0.0770249</t>
         </is>
       </c>
       <c r="R68" s="2" t="n">
@@ -5020,11 +5020,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -5091,11 +5091,11 @@
         <v>0.7062841238960693</v>
       </c>
       <c r="P70" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07169789949000656</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.706284 ± 0</t>
+          <t xml:space="preserve">0.706284 ± 0.0716979</t>
         </is>
       </c>
       <c r="R70" s="2" t="n">
@@ -5162,11 +5162,11 @@
         <v>0.2471278375149343</v>
       </c>
       <c r="P71" t="n">
-        <v>0.0</v>
+        <v>0.1470621192076721</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.247128 ± 0</t>
+          <t xml:space="preserve">0.247128 ± 0.147062</t>
         </is>
       </c>
       <c r="R71" t="n">
@@ -5233,11 +5233,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P72" s="2" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R72" s="2" t="n">
@@ -5304,11 +5304,11 @@
         <v>0.599378733572282</v>
       </c>
       <c r="P73" t="n">
-        <v>0.0</v>
+        <v>0.11198285627460437</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599379 ± 0</t>
+          <t xml:space="preserve">0.599379 ± 0.111983</t>
         </is>
       </c>
       <c r="R73" t="n">
@@ -5375,11 +5375,11 @@
         <v>0.1058333333333334</v>
       </c>
       <c r="P74" s="2" t="n">
-        <v>0.0</v>
+        <v>0.11612332425822823</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.105833 ± 0</t>
+          <t xml:space="preserve">0.105833 ± 0.116123</t>
         </is>
       </c>
       <c r="R74" s="2" t="n">
@@ -5446,11 +5446,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R75" t="n">
@@ -5517,11 +5517,11 @@
         <v>0.715</v>
       </c>
       <c r="P76" s="2" t="n">
-        <v>0.0</v>
+        <v>0.1108509406116284</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715 ± 0</t>
+          <t xml:space="preserve">0.715 ± 0.110851</t>
         </is>
       </c>
       <c r="R76" s="2" t="n">
@@ -5659,11 +5659,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P78" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R78" s="2" t="n">
@@ -5872,11 +5872,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P81" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R81" t="n">
@@ -6085,11 +6085,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R84" s="2" t="n">
@@ -6298,11 +6298,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P87" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -6511,11 +6511,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R90" s="2" t="n">
@@ -6724,11 +6724,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P93" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R93" t="n">
@@ -6937,11 +6937,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R96" s="2" t="n">
@@ -7150,11 +7150,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R99" t="n">
@@ -7363,11 +7363,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P102" s="2" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R102" s="2" t="n">
@@ -7576,11 +7576,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P105" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -7789,11 +7789,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R108" s="2" t="n">
@@ -8002,11 +8002,11 @@
         <v>0.8177893781482453</v>
       </c>
       <c r="P111" t="n">
-        <v>0.0</v>
+        <v>0.027447766939561757</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.817789 ± 0</t>
+          <t xml:space="preserve">0.817789 ± 0.0274478</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -8215,11 +8215,11 @@
         <v>0.8222603288494496</v>
       </c>
       <c r="P114" s="2" t="n">
-        <v>0.0</v>
+        <v>0.028146932745030495</v>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.82226 ± 0</t>
+          <t xml:space="preserve">0.82226 ± 0.0281469</t>
         </is>
       </c>
       <c r="R114" s="2" t="n">
@@ -8428,11 +8428,11 @@
         <v>0.8465065710872162</v>
       </c>
       <c r="P117" t="n">
-        <v>0.0</v>
+        <v>0.09532631749119894</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.846507 ± 0</t>
+          <t xml:space="preserve">0.846507 ± 0.0953263</t>
         </is>
       </c>
       <c r="R117" t="n">
@@ -8641,11 +8641,11 @@
         <v>0.8208333333333334</v>
       </c>
       <c r="P120" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03459328550887946</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820833 ± 0</t>
+          <t xml:space="preserve">0.820833 ± 0.0345933</t>
         </is>
       </c>
       <c r="R120" s="2" t="n">
@@ -8854,11 +8854,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P123" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R123" t="n">
@@ -9067,11 +9067,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P126" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R126" s="2" t="n">
@@ -9280,11 +9280,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P129" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R129" t="n">
@@ -9493,11 +9493,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -9706,11 +9706,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P135" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R135" t="n">
@@ -9919,11 +9919,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P138" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R138" s="2" t="n">
@@ -10132,11 +10132,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P141" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R141" t="n">
@@ -10345,11 +10345,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P144" s="2" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R144" s="2" t="n">
@@ -10558,11 +10558,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P147" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R147" t="n">
@@ -10771,11 +10771,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P150" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R150" s="2" t="n">
@@ -10984,11 +10984,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P153" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R153" t="n">
@@ -11197,11 +11197,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P156" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R156" s="2" t="n">
@@ -11410,11 +11410,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P159" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R159" t="n">
@@ -11623,11 +11623,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P162" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R162" s="2" t="n">
@@ -11836,11 +11836,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P165" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R165" t="n">
@@ -12049,11 +12049,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P168" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R168" s="2" t="n">
@@ -12262,11 +12262,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P171" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R171" t="n">
@@ -12475,11 +12475,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P174" s="2" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q174" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R174" s="2" t="n">
@@ -12688,11 +12688,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P177" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R177" t="n">
@@ -12901,11 +12901,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P180" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R180" s="2" t="n">
@@ -13043,11 +13043,11 @@
         <v>0.131578947368421</v>
       </c>
       <c r="P182" s="2" t="n">
-        <v>0.0</v>
+        <v>0.08263951626676193</v>
       </c>
       <c r="Q182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.131579 ± 0</t>
+          <t xml:space="preserve">0.131579 ± 0.0826395</t>
         </is>
       </c>
       <c r="R182" s="2" t="n">
@@ -13114,11 +13114,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P183" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R183" t="n">
@@ -13185,11 +13185,11 @@
         <v>0.7942982456140352</v>
       </c>
       <c r="P184" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07699362077068307</v>
       </c>
       <c r="Q184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.794298 ± 0</t>
+          <t xml:space="preserve">0.794298 ± 0.0769936</t>
         </is>
       </c>
       <c r="R184" s="2" t="n">
@@ -13256,11 +13256,11 @@
         <v>0.13268295619056225</v>
       </c>
       <c r="P185" t="n">
-        <v>0.0</v>
+        <v>0.08290776860666817</v>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.132683 ± 0</t>
+          <t xml:space="preserve">0.132683 ± 0.0829078</t>
         </is>
       </c>
       <c r="R185" t="n">
@@ -13327,11 +13327,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P186" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R186" s="2" t="n">
@@ -13398,11 +13398,11 @@
         <v>0.7931269372831096</v>
       </c>
       <c r="P187" t="n">
-        <v>0.0</v>
+        <v>0.07724434998893068</v>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793127 ± 0</t>
+          <t xml:space="preserve">0.793127 ± 0.0772443</t>
         </is>
       </c>
       <c r="R187" t="n">
@@ -13469,11 +13469,11 @@
         <v>0.12817053785613117</v>
       </c>
       <c r="P188" s="2" t="n">
-        <v>0.0</v>
+        <v>0.08430573709398424</v>
       </c>
       <c r="Q188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.128171 ± 0</t>
+          <t xml:space="preserve">0.128171 ± 0.0843057</t>
         </is>
       </c>
       <c r="R188" s="2" t="n">
@@ -13540,11 +13540,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P189" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R189" t="n">
@@ -13611,11 +13611,11 @@
         <v>0.7989688621478904</v>
       </c>
       <c r="P190" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07878976906185375</v>
       </c>
       <c r="Q190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.798969 ± 0</t>
+          <t xml:space="preserve">0.798969 ± 0.0787898</t>
         </is>
       </c>
       <c r="R190" s="2" t="n">
@@ -13682,11 +13682,11 @@
         <v>0.09072534072534075</v>
       </c>
       <c r="P191" t="n">
-        <v>0.0</v>
+        <v>0.116106979590653</v>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0907253 ± 0</t>
+          <t xml:space="preserve">0.0907253 ± 0.116107</t>
         </is>
       </c>
       <c r="R191" t="n">
@@ -13753,11 +13753,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P192" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q192" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R192" s="2" t="n">
@@ -13824,11 +13824,11 @@
         <v>0.8443173943173944</v>
       </c>
       <c r="P193" t="n">
-        <v>0.0</v>
+        <v>0.10975281514523044</v>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.844317 ± 0</t>
+          <t xml:space="preserve">0.844317 ± 0.109753</t>
         </is>
       </c>
       <c r="R193" t="n">
@@ -13895,11 +13895,11 @@
         <v>0.131578947368421</v>
       </c>
       <c r="P194" s="2" t="n">
-        <v>0.0</v>
+        <v>0.08263951626676193</v>
       </c>
       <c r="Q194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.131579 ± 0</t>
+          <t xml:space="preserve">0.131579 ± 0.0826395</t>
         </is>
       </c>
       <c r="R194" s="2" t="n">
@@ -13966,11 +13966,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P195" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R195" t="n">
@@ -14037,11 +14037,11 @@
         <v>0.7942982456140352</v>
       </c>
       <c r="P196" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07699362077068307</v>
       </c>
       <c r="Q196" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.794298 ± 0</t>
+          <t xml:space="preserve">0.794298 ± 0.0769936</t>
         </is>
       </c>
       <c r="R196" s="2" t="n">
@@ -14179,11 +14179,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P198" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q198" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R198" s="2" t="n">
@@ -14392,11 +14392,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P201" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q201" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R201" t="n">
@@ -14605,11 +14605,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P204" s="2" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R204" s="2" t="n">
@@ -14818,11 +14818,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P207" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R207" t="n">
@@ -15031,11 +15031,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P210" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R210" s="2" t="n">
@@ -15244,11 +15244,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P213" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R213" t="n">
@@ -15457,11 +15457,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P216" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R216" s="2" t="n">
@@ -15670,11 +15670,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P219" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R219" t="n">
@@ -15883,11 +15883,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P222" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R222" s="2" t="n">
@@ -16096,11 +16096,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P225" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R225" t="n">
@@ -16309,11 +16309,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P228" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R228" s="2" t="n">
@@ -16522,11 +16522,11 @@
         <v>0.9258098934736715</v>
       </c>
       <c r="P231" t="n">
-        <v>0.0</v>
+        <v>0.030116581647398454</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.92581 ± 0</t>
+          <t xml:space="preserve">0.92581 ± 0.0301166</t>
         </is>
       </c>
       <c r="R231" t="n">
@@ -16735,11 +16735,11 @@
         <v>0.9271394000040216</v>
       </c>
       <c r="P234" s="2" t="n">
-        <v>0.0</v>
+        <v>0.02999382600035785</v>
       </c>
       <c r="Q234" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927139 ± 0</t>
+          <t xml:space="preserve">0.927139 ± 0.0299938</t>
         </is>
       </c>
       <c r="R234" s="2" t="n">
@@ -16948,11 +16948,11 @@
         <v>0.935042735042735</v>
       </c>
       <c r="P237" t="n">
-        <v>0.0</v>
+        <v>0.037883377322530096</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.935043 ± 0</t>
+          <t xml:space="preserve">0.935043 ± 0.0378834</t>
         </is>
       </c>
       <c r="R237" t="n">
@@ -17161,11 +17161,11 @@
         <v>0.9258771929824562</v>
       </c>
       <c r="P240" s="2" t="n">
-        <v>0.0</v>
+        <v>0.030021192671588672</v>
       </c>
       <c r="Q240" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925877 ± 0</t>
+          <t xml:space="preserve">0.925877 ± 0.0300212</t>
         </is>
       </c>
       <c r="R240" s="2" t="n">
@@ -17374,11 +17374,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P243" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R243" t="n">
@@ -17587,11 +17587,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P246" s="2" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R246" s="2" t="n">
@@ -17800,11 +17800,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P249" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R249" t="n">
@@ -18013,11 +18013,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P252" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q252" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R252" s="2" t="n">
@@ -18226,11 +18226,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P255" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R255" t="n">
@@ -18439,11 +18439,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P258" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R258" s="2" t="n">
@@ -18652,11 +18652,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P261" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R261" t="n">
@@ -18865,11 +18865,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P264" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R264" s="2" t="n">
@@ -19078,11 +19078,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P267" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R267" t="n">
@@ -19291,11 +19291,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P270" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R270" s="2" t="n">
@@ -19504,11 +19504,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P273" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R273" t="n">
@@ -19717,11 +19717,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P276" s="2" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R276" s="2" t="n">
@@ -19930,11 +19930,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P279" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R279" t="n">
@@ -20143,11 +20143,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P282" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q282" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R282" s="2" t="n">
@@ -20356,11 +20356,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P285" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R285" t="n">
@@ -20569,11 +20569,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P288" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R288" s="2" t="n">
@@ -20782,11 +20782,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P291" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R291" t="n">
@@ -20995,11 +20995,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P294" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R294" s="2" t="n">
@@ -21208,11 +21208,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P297" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R297" t="n">
@@ -21421,11 +21421,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P300" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R300" s="2" t="n">
@@ -21563,11 +21563,11 @@
         <v>0.027166666666666665</v>
       </c>
       <c r="P302" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04673260940295539</v>
       </c>
       <c r="Q302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0271667 ± 0</t>
+          <t xml:space="preserve">0.0271667 ± 0.0467326</t>
         </is>
       </c>
       <c r="R302" s="2" t="n">
@@ -21634,11 +21634,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P303" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R303" t="n">
@@ -21705,11 +21705,11 @@
         <v>0.8425</v>
       </c>
       <c r="P304" s="2" t="n">
-        <v>0.0</v>
+        <v>0.043899375535578995</v>
       </c>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8425 ± 0</t>
+          <t xml:space="preserve">0.8425 ± 0.0438994</t>
         </is>
       </c>
       <c r="R304" s="2" t="n">
@@ -21776,11 +21776,11 @@
         <v>0.0413875842173721</v>
       </c>
       <c r="P305" t="n">
-        <v>0.0</v>
+        <v>0.027344387641327284</v>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0413876 ± 0</t>
+          <t xml:space="preserve">0.0413876 ± 0.0273444</t>
         </is>
       </c>
       <c r="R305" t="n">
@@ -21847,11 +21847,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P306" s="2" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q306" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R306" s="2" t="n">
@@ -21918,11 +21918,11 @@
         <v>0.8063256948285245</v>
       </c>
       <c r="P307" t="n">
-        <v>0.0</v>
+        <v>0.014177393042292909</v>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.806326 ± 0</t>
+          <t xml:space="preserve">0.806326 ± 0.0141774</t>
         </is>
       </c>
       <c r="R307" t="n">
@@ -21989,11 +21989,11 @@
         <v>0.06451088920761827</v>
       </c>
       <c r="P308" s="2" t="n">
-        <v>0.0</v>
+        <v>0.034993597205544444</v>
       </c>
       <c r="Q308" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0645109 ± 0</t>
+          <t xml:space="preserve">0.0645109 ± 0.0349936</t>
         </is>
       </c>
       <c r="R308" s="2" t="n">
@@ -22060,11 +22060,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P309" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R309" t="n">
@@ -22131,11 +22131,11 @@
         <v>0.7750046459688701</v>
       </c>
       <c r="P310" s="2" t="n">
-        <v>0.0</v>
+        <v>0.014354174090147989</v>
       </c>
       <c r="Q310" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.775005 ± 0</t>
+          <t xml:space="preserve">0.775005 ± 0.0143542</t>
         </is>
       </c>
       <c r="R310" s="2" t="n">
@@ -22202,11 +22202,11 @@
         <v>0.1342514285714287</v>
       </c>
       <c r="P311" t="n">
-        <v>0.0</v>
+        <v>0.15353267530130113</v>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.134251 ± 0</t>
+          <t xml:space="preserve">0.134251 ± 0.153533</t>
         </is>
       </c>
       <c r="R311" t="n">
@@ -22273,11 +22273,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P312" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R312" s="2" t="n">
@@ -22344,11 +22344,11 @@
         <v>0.6800647619047616</v>
       </c>
       <c r="P313" t="n">
-        <v>0.0</v>
+        <v>0.1087059563061277</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.680065 ± 0</t>
+          <t xml:space="preserve">0.680065 ± 0.108706</t>
         </is>
       </c>
       <c r="R313" t="n">
@@ -22415,11 +22415,11 @@
         <v>0.027166666666666665</v>
       </c>
       <c r="P314" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04673260940295539</v>
       </c>
       <c r="Q314" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0271667 ± 0</t>
+          <t xml:space="preserve">0.0271667 ± 0.0467326</t>
         </is>
       </c>
       <c r="R314" s="2" t="n">
@@ -22486,11 +22486,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P315" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R315" t="n">
@@ -22557,11 +22557,11 @@
         <v>0.8425</v>
       </c>
       <c r="P316" s="2" t="n">
-        <v>0.0</v>
+        <v>0.043899375535578995</v>
       </c>
       <c r="Q316" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8425 ± 0</t>
+          <t xml:space="preserve">0.8425 ± 0.0438994</t>
         </is>
       </c>
       <c r="R316" s="2" t="n">
@@ -22699,11 +22699,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P318" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q318" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R318" s="2" t="n">
@@ -22912,11 +22912,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P321" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R321" t="n">
@@ -23125,11 +23125,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P324" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q324" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R324" s="2" t="n">
@@ -23338,11 +23338,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P327" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q327" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R327" t="n">
@@ -23551,11 +23551,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P330" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q330" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R330" s="2" t="n">
@@ -23764,11 +23764,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P333" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R333" t="n">
@@ -23977,11 +23977,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P336" s="2" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q336" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R336" s="2" t="n">
@@ -24190,11 +24190,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P339" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R339" t="n">
@@ -24403,11 +24403,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P342" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R342" s="2" t="n">
@@ -24616,11 +24616,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P345" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R345" t="n">
@@ -24823,11 +24823,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P348" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q348" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R348" s="2" t="n">
@@ -25024,11 +25024,11 @@
         <v>0.8477132790458966</v>
       </c>
       <c r="P351" t="n">
-        <v>0.0</v>
+        <v>0.023381981567085305</v>
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.847713 ± 0</t>
+          <t xml:space="preserve">0.847713 ± 0.023382</t>
         </is>
       </c>
       <c r="R351" t="n">
@@ -25225,11 +25225,11 @@
         <v>0.8395155351764882</v>
       </c>
       <c r="P354" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03191409612653337</v>
       </c>
       <c r="Q354" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.839516 ± 0</t>
+          <t xml:space="preserve">0.839516 ± 0.0319141</t>
         </is>
       </c>
       <c r="R354" s="2" t="n">
@@ -25426,11 +25426,11 @@
         <v>0.8143161904761904</v>
       </c>
       <c r="P357" t="n">
-        <v>0.0</v>
+        <v>0.10842184949882111</v>
       </c>
       <c r="Q357" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.814316 ± 0</t>
+          <t xml:space="preserve">0.814316 ± 0.108422</t>
         </is>
       </c>
       <c r="R357" t="n">
@@ -25627,11 +25627,11 @@
         <v>0.8696666666666667</v>
       </c>
       <c r="P360" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01602440667217987</v>
       </c>
       <c r="Q360" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.869667 ± 0</t>
+          <t xml:space="preserve">0.869667 ± 0.0160244</t>
         </is>
       </c>
       <c r="R360" s="2" t="n">
@@ -25834,11 +25834,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P363" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R363" t="n">
@@ -26047,11 +26047,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P366" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q366" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R366" s="2" t="n">
@@ -26260,11 +26260,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P369" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R369" t="n">
@@ -26473,11 +26473,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P372" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q372" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R372" s="2" t="n">
@@ -26686,11 +26686,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P375" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q375" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R375" t="n">
@@ -26899,11 +26899,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P378" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q378" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R378" s="2" t="n">
@@ -27112,11 +27112,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P381" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q381" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R381" t="n">
@@ -27325,11 +27325,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P384" s="2" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q384" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R384" s="2" t="n">
@@ -27538,11 +27538,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P387" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R387" t="n">
@@ -27751,11 +27751,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P390" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q390" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R390" s="2" t="n">
@@ -27964,11 +27964,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P393" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R393" t="n">
@@ -28177,11 +28177,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P396" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q396" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R396" s="2" t="n">
@@ -28390,11 +28390,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P399" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R399" t="n">
@@ -28603,11 +28603,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P402" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q402" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R402" s="2" t="n">
@@ -28816,11 +28816,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P405" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R405" t="n">
@@ -29029,11 +29029,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P408" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q408" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R408" s="2" t="n">
@@ -29242,11 +29242,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P411" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q411" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R411" t="n">
@@ -29455,11 +29455,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P414" s="2" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q414" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R414" s="2" t="n">
@@ -29668,11 +29668,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P417" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R417" t="n">
@@ -29881,11 +29881,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P420" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q420" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R420" s="2" t="n">
@@ -30023,11 +30023,11 @@
         <v>0.01973333333333338</v>
       </c>
       <c r="P422" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0718122232095543</v>
       </c>
       <c r="Q422" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0197333 ± 0</t>
+          <t xml:space="preserve">0.0197333 ± 0.0718122</t>
         </is>
       </c>
       <c r="R422" s="2" t="n">
@@ -30094,11 +30094,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P423" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R423" t="n">
@@ -30165,11 +30165,11 @@
         <v>0.8111666666666666</v>
       </c>
       <c r="P424" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06124911446697419</v>
       </c>
       <c r="Q424" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.811167 ± 0</t>
+          <t xml:space="preserve">0.811167 ± 0.0612491</t>
         </is>
       </c>
       <c r="R424" s="2" t="n">
@@ -30236,11 +30236,11 @@
         <v>0.0197923324797088</v>
       </c>
       <c r="P425" t="n">
-        <v>0.0</v>
+        <v>0.029000316657020766</v>
       </c>
       <c r="Q425" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0197923 ± 0</t>
+          <t xml:space="preserve">0.0197923 ± 0.0290003</t>
         </is>
       </c>
       <c r="R425" t="n">
@@ -30307,11 +30307,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P426" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q426" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R426" s="2" t="n">
@@ -30378,11 +30378,11 @@
         <v>0.783562273511986</v>
       </c>
       <c r="P427" t="n">
-        <v>0.0</v>
+        <v>0.025476267844788958</v>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.783562 ± 0</t>
+          <t xml:space="preserve">0.783562 ± 0.0254763</t>
         </is>
       </c>
       <c r="R427" t="n">
@@ -30449,11 +30449,11 @@
         <v>0.02402557857830812</v>
       </c>
       <c r="P428" s="2" t="n">
-        <v>0.0</v>
+        <v>0.015987084756551126</v>
       </c>
       <c r="Q428" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0240256 ± 0</t>
+          <t xml:space="preserve">0.0240256 ± 0.0159871</t>
         </is>
       </c>
       <c r="R428" s="2" t="n">
@@ -30520,11 +30520,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P429" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q429" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R429" t="n">
@@ -30591,11 +30591,11 @@
         <v>0.7757480119951818</v>
       </c>
       <c r="P430" s="2" t="n">
-        <v>0.0</v>
+        <v>0.010193106119050974</v>
       </c>
       <c r="Q430" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.775748 ± 0</t>
+          <t xml:space="preserve">0.775748 ± 0.0101931</t>
         </is>
       </c>
       <c r="R430" s="2" t="n">
@@ -30662,11 +30662,11 @@
         <v>0.06270259591781846</v>
       </c>
       <c r="P431" t="n">
-        <v>0.0</v>
+        <v>0.14036664742368077</v>
       </c>
       <c r="Q431" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0627026 ± 0</t>
+          <t xml:space="preserve">0.0627026 ± 0.140367</t>
         </is>
       </c>
       <c r="R431" t="n">
@@ -30733,11 +30733,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P432" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q432" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R432" s="2" t="n">
@@ -30804,11 +30804,11 @@
         <v>0.6526816638084669</v>
       </c>
       <c r="P433" t="n">
-        <v>0.0</v>
+        <v>0.09131978113322538</v>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.652682 ± 0</t>
+          <t xml:space="preserve">0.652682 ± 0.0913198</t>
         </is>
       </c>
       <c r="R433" t="n">
@@ -30875,11 +30875,11 @@
         <v>0.01973333333333338</v>
       </c>
       <c r="P434" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0718122232095543</v>
       </c>
       <c r="Q434" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0197333 ± 0</t>
+          <t xml:space="preserve">0.0197333 ± 0.0718122</t>
         </is>
       </c>
       <c r="R434" s="2" t="n">
@@ -30946,11 +30946,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P435" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q435" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R435" t="n">
@@ -31017,11 +31017,11 @@
         <v>0.8111666666666666</v>
       </c>
       <c r="P436" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06124911446697419</v>
       </c>
       <c r="Q436" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.811167 ± 0</t>
+          <t xml:space="preserve">0.811167 ± 0.0612491</t>
         </is>
       </c>
       <c r="R436" s="2" t="n">
@@ -31159,11 +31159,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P438" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q438" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R438" s="2" t="n">
@@ -31372,11 +31372,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P441" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R441" t="n">
@@ -31585,11 +31585,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P444" s="2" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q444" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R444" s="2" t="n">
@@ -31798,11 +31798,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P447" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R447" t="n">
@@ -32011,11 +32011,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P450" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q450" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R450" s="2" t="n">
@@ -32224,11 +32224,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P453" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q453" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R453" t="n">
@@ -32437,11 +32437,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P456" s="2" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q456" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R456" s="2" t="n">
@@ -32650,11 +32650,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P459" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q459" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R459" t="n">
@@ -32863,11 +32863,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P462" s="2" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q462" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R462" s="2" t="n">
@@ -33076,11 +33076,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P465" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R465" t="n">
@@ -33289,11 +33289,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P468" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q468" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R468" s="2" t="n">
@@ -33502,11 +33502,11 @@
         <v>0.8033546059916947</v>
       </c>
       <c r="P471" t="n">
-        <v>0.0</v>
+        <v>0.01385561773823341</v>
       </c>
       <c r="Q471" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.803355 ± 0</t>
+          <t xml:space="preserve">0.803355 ± 0.0138556</t>
         </is>
       </c>
       <c r="R471" t="n">
@@ -33715,11 +33715,11 @@
         <v>0.79977359057349</v>
       </c>
       <c r="P474" s="2" t="n">
-        <v>0.0</v>
+        <v>0.012316146583201865</v>
       </c>
       <c r="Q474" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.799774 ± 0</t>
+          <t xml:space="preserve">0.799774 ± 0.0123161</t>
         </is>
       </c>
       <c r="R474" s="2" t="n">
@@ -33928,11 +33928,11 @@
         <v>0.7153842597262854</v>
       </c>
       <c r="P477" t="n">
-        <v>0.0</v>
+        <v>0.10659968706681891</v>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.715384 ± 0</t>
+          <t xml:space="preserve">0.715384 ± 0.1066</t>
         </is>
       </c>
       <c r="R477" t="n">
@@ -34141,11 +34141,11 @@
         <v>0.8309000000000001</v>
       </c>
       <c r="P480" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037490550533572364</v>
       </c>
       <c r="Q480" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.8309 ± 0</t>
+          <t xml:space="preserve">0.8309 ± 0.0374906</t>
         </is>
       </c>
       <c r="R480" s="2" t="n">
@@ -34993,11 +34993,11 @@
         <v>0.9709325396825397</v>
       </c>
       <c r="P492" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q492" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R492" s="2" t="n">
@@ -36046,11 +36046,11 @@
         <v>0.9709325396825398</v>
       </c>
       <c r="P507" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q507" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R507" t="n">
@@ -37105,11 +37105,11 @@
         <v>0.9709325396825397</v>
       </c>
       <c r="P522" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q522" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R522" s="2" t="n">
@@ -38170,11 +38170,11 @@
         <v>0.9709325396825397</v>
       </c>
       <c r="P537" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q537" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R537" t="n">
@@ -38667,11 +38667,11 @@
         <v>0.7973684210526314</v>
       </c>
       <c r="P544" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05801971880526742</v>
       </c>
       <c r="Q544" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.797368 ± 0</t>
+          <t xml:space="preserve">0.797368 ± 0.0580197</t>
         </is>
       </c>
       <c r="R544" s="2" t="n">
@@ -38880,11 +38880,11 @@
         <v>0.7917795905744779</v>
       </c>
       <c r="P547" t="n">
-        <v>0.0</v>
+        <v>0.05312542924209885</v>
       </c>
       <c r="Q547" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.79178 ± 0</t>
+          <t xml:space="preserve">0.79178 ± 0.0531254</t>
         </is>
       </c>
       <c r="R547" t="n">
@@ -39093,11 +39093,11 @@
         <v>0.8081539513676577</v>
       </c>
       <c r="P550" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06221446481402166</v>
       </c>
       <c r="Q550" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.808154 ± 0</t>
+          <t xml:space="preserve">0.808154 ± 0.0622145</t>
         </is>
       </c>
       <c r="R550" s="2" t="n">
@@ -39235,11 +39235,11 @@
         <v>0.9709325396825397</v>
       </c>
       <c r="P552" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q552" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R552" s="2" t="n">
@@ -39519,11 +39519,11 @@
         <v>0.7973684210526314</v>
       </c>
       <c r="P556" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05801971880526742</v>
       </c>
       <c r="Q556" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.797368 ± 0</t>
+          <t xml:space="preserve">0.797368 ± 0.0580197</t>
         </is>
       </c>
       <c r="R556" s="2" t="n">
@@ -40300,11 +40300,11 @@
         <v>0.9709325396825397</v>
       </c>
       <c r="P567" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q567" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R567" t="n">
@@ -41365,11 +41365,11 @@
         <v>0.9709325396825397</v>
       </c>
       <c r="P582" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q582" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R582" s="2" t="n">
@@ -42430,11 +42430,11 @@
         <v>0.9709325396825397</v>
       </c>
       <c r="P597" t="n">
-        <v>0.0</v>
+        <v>0.03538483407819295</v>
       </c>
       <c r="Q597" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.970933 ± 0</t>
+          <t xml:space="preserve">0.970933 ± 0.0353848</t>
         </is>
       </c>
       <c r="R597" t="n">
@@ -42856,11 +42856,11 @@
         <v>0.7358</v>
       </c>
       <c r="P603" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q603" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R603" t="n">
@@ -43069,11 +43069,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P606" s="2" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q606" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R606" s="2" t="n">
@@ -43282,11 +43282,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P609" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q609" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R609" t="n">
@@ -43708,11 +43708,11 @@
         <v>0.7358</v>
       </c>
       <c r="P615" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q615" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R615" t="n">
@@ -43921,11 +43921,11 @@
         <v>0.7358</v>
       </c>
       <c r="P618" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q618" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R618" s="2" t="n">
@@ -44134,11 +44134,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P621" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q621" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R621" t="n">
@@ -44347,11 +44347,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P624" s="2" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q624" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R624" s="2" t="n">
@@ -44773,11 +44773,11 @@
         <v>0.7358</v>
       </c>
       <c r="P630" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q630" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R630" s="2" t="n">
@@ -44986,11 +44986,11 @@
         <v>0.7358</v>
       </c>
       <c r="P633" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q633" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R633" t="n">
@@ -45199,11 +45199,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P636" s="2" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q636" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R636" s="2" t="n">
@@ -45412,11 +45412,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P639" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q639" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R639" t="n">
@@ -45838,11 +45838,11 @@
         <v>0.7358</v>
       </c>
       <c r="P645" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q645" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R645" t="n">
@@ -46051,11 +46051,11 @@
         <v>0.7358</v>
       </c>
       <c r="P648" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q648" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R648" s="2" t="n">
@@ -46264,11 +46264,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P651" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q651" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R651" t="n">
@@ -46477,11 +46477,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P654" s="2" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q654" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R654" s="2" t="n">
@@ -46903,11 +46903,11 @@
         <v>0.7358</v>
       </c>
       <c r="P660" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q660" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R660" s="2" t="n">
@@ -47045,11 +47045,11 @@
         <v>0.19243333333333307</v>
       </c>
       <c r="P662" s="2" t="n">
-        <v>0.0</v>
+        <v>0.09431564149113898</v>
       </c>
       <c r="Q662" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.192433 ± 0</t>
+          <t xml:space="preserve">0.192433 ± 0.0943156</t>
         </is>
       </c>
       <c r="R662" s="2" t="n">
@@ -47116,11 +47116,11 @@
         <v>0.7358</v>
       </c>
       <c r="P663" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q663" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R663" t="n">
@@ -47187,11 +47187,11 @@
         <v>0.5433666666666668</v>
       </c>
       <c r="P664" s="2" t="n">
-        <v>0.0</v>
+        <v>0.08654218956504765</v>
       </c>
       <c r="Q664" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.543367 ± 0</t>
+          <t xml:space="preserve">0.543367 ± 0.0865422</t>
         </is>
       </c>
       <c r="R664" s="2" t="n">
@@ -47258,11 +47258,11 @@
         <v>0.2225496466401143</v>
       </c>
       <c r="P665" t="n">
-        <v>0.0</v>
+        <v>0.07410473000823212</v>
       </c>
       <c r="Q665" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.22255 ± 0</t>
+          <t xml:space="preserve">0.22255 ± 0.0741047</t>
         </is>
       </c>
       <c r="R665" t="n">
@@ -47329,11 +47329,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P666" s="2" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q666" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R666" s="2" t="n">
@@ -47400,11 +47400,11 @@
         <v>0.5061623646775353</v>
       </c>
       <c r="P667" t="n">
-        <v>0.0</v>
+        <v>0.06598453616956677</v>
       </c>
       <c r="Q667" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.506162 ± 0</t>
+          <t xml:space="preserve">0.506162 ± 0.0659845</t>
         </is>
       </c>
       <c r="R667" t="n">
@@ -47471,11 +47471,11 @@
         <v>0.23566685494330813</v>
       </c>
       <c r="P668" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06951625693533824</v>
       </c>
       <c r="Q668" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.235667 ± 0</t>
+          <t xml:space="preserve">0.235667 ± 0.0695163</t>
         </is>
       </c>
       <c r="R668" s="2" t="n">
@@ -47542,11 +47542,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P669" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q669" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R669" t="n">
@@ -47613,11 +47613,11 @@
         <v>0.4939750849532495</v>
       </c>
       <c r="P670" s="2" t="n">
-        <v>0.0</v>
+        <v>0.057440028997199154</v>
       </c>
       <c r="Q670" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.493975 ± 0</t>
+          <t xml:space="preserve">0.493975 ± 0.05744</t>
         </is>
       </c>
       <c r="R670" s="2" t="n">
@@ -47826,11 +47826,11 @@
         <v>0.6551490872391356</v>
       </c>
       <c r="P673" t="n">
-        <v>0.0</v>
+        <v>0.08113700504826853</v>
       </c>
       <c r="Q673" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.655149 ± 0</t>
+          <t xml:space="preserve">0.655149 ± 0.081137</t>
         </is>
       </c>
       <c r="R673" t="n">
@@ -47897,11 +47897,11 @@
         <v>0.19243333333333307</v>
       </c>
       <c r="P674" s="2" t="n">
-        <v>0.0</v>
+        <v>0.09431564149113898</v>
       </c>
       <c r="Q674" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.192433 ± 0</t>
+          <t xml:space="preserve">0.192433 ± 0.0943156</t>
         </is>
       </c>
       <c r="R674" s="2" t="n">
@@ -47968,11 +47968,11 @@
         <v>0.7358</v>
       </c>
       <c r="P675" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q675" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R675" t="n">
@@ -48039,11 +48039,11 @@
         <v>0.5433666666666668</v>
       </c>
       <c r="P676" s="2" t="n">
-        <v>0.0</v>
+        <v>0.08654218956504765</v>
       </c>
       <c r="Q676" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.543367 ± 0</t>
+          <t xml:space="preserve">0.543367 ± 0.0865422</t>
         </is>
       </c>
       <c r="R676" s="2" t="n">
@@ -48181,11 +48181,11 @@
         <v>0.7358</v>
       </c>
       <c r="P678" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q678" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R678" s="2" t="n">
@@ -48394,11 +48394,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P681" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q681" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R681" t="n">
@@ -48607,11 +48607,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P684" s="2" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q684" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R684" s="2" t="n">
@@ -49021,11 +49021,11 @@
         <v>0.7358</v>
       </c>
       <c r="P690" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q690" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R690" s="2" t="n">
@@ -49234,11 +49234,11 @@
         <v>0.7358</v>
       </c>
       <c r="P693" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q693" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R693" t="n">
@@ -49447,11 +49447,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P696" s="2" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q696" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R696" s="2" t="n">
@@ -49660,11 +49660,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P699" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q699" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R699" t="n">
@@ -50082,11 +50082,11 @@
         <v>0.7358</v>
       </c>
       <c r="P705" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q705" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R705" t="n">
@@ -50295,11 +50295,11 @@
         <v>0.7358</v>
       </c>
       <c r="P708" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q708" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R708" s="2" t="n">
@@ -50508,11 +50508,11 @@
         <v>0.7287120113176496</v>
       </c>
       <c r="P711" t="n">
-        <v>0.0</v>
+        <v>0.033727614740448414</v>
       </c>
       <c r="Q711" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.728712 ± 0</t>
+          <t xml:space="preserve">0.728712 ± 0.0337276</t>
         </is>
       </c>
       <c r="R711" t="n">
@@ -50721,11 +50721,11 @@
         <v>0.7296419398965577</v>
       </c>
       <c r="P714" s="2" t="n">
-        <v>0.0</v>
+        <v>0.039155498299739244</v>
       </c>
       <c r="Q714" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.729642 ± 0</t>
+          <t xml:space="preserve">0.729642 ± 0.0391555</t>
         </is>
       </c>
       <c r="R714" s="2" t="n">
@@ -51147,11 +51147,11 @@
         <v>0.7358</v>
       </c>
       <c r="P720" s="2" t="n">
-        <v>0.0</v>
+        <v>0.037495195094470635</v>
       </c>
       <c r="Q720" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.7358 ± 0</t>
+          <t xml:space="preserve">0.7358 ± 0.0374952</t>
         </is>
       </c>
       <c r="R720" s="2" t="n">
@@ -51360,11 +51360,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P723" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q723" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R723" t="n">
@@ -51573,11 +51573,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P726" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q726" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R726" s="2" t="n">
@@ -51786,11 +51786,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P729" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q729" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R729" t="n">
@@ -51999,11 +51999,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P732" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q732" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R732" s="2" t="n">
@@ -52212,11 +52212,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P735" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q735" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R735" t="n">
@@ -52425,11 +52425,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P738" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q738" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R738" s="2" t="n">
@@ -52638,11 +52638,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P741" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q741" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R741" t="n">
@@ -52851,11 +52851,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P744" s="2" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q744" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R744" s="2" t="n">
@@ -53064,11 +53064,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P747" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q747" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R747" t="n">
@@ -53277,11 +53277,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P750" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q750" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R750" s="2" t="n">
@@ -53490,11 +53490,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P753" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q753" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R753" t="n">
@@ -53703,11 +53703,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P756" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q756" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R756" s="2" t="n">
@@ -53916,11 +53916,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P759" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q759" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R759" t="n">
@@ -54129,11 +54129,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P762" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q762" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R762" s="2" t="n">
@@ -54342,11 +54342,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P765" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q765" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R765" t="n">
@@ -54555,11 +54555,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P768" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q768" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R768" s="2" t="n">
@@ -54768,11 +54768,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P771" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q771" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R771" t="n">
@@ -54981,11 +54981,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P774" s="2" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q774" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R774" s="2" t="n">
@@ -55194,11 +55194,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P777" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q777" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R777" t="n">
@@ -55407,11 +55407,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P780" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q780" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R780" s="2" t="n">
@@ -55549,11 +55549,11 @@
         <v>0.08416666666666661</v>
       </c>
       <c r="P782" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05145944726329341</v>
       </c>
       <c r="Q782" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0841667 ± 0</t>
+          <t xml:space="preserve">0.0841667 ± 0.0514594</t>
         </is>
       </c>
       <c r="R782" s="2" t="n">
@@ -55620,11 +55620,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P783" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q783" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R783" t="n">
@@ -55691,11 +55691,11 @@
         <v>0.709</v>
       </c>
       <c r="P784" s="2" t="n">
-        <v>0.0</v>
+        <v>0.035752983960348886</v>
       </c>
       <c r="Q784" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.709 ± 0</t>
+          <t xml:space="preserve">0.709 ± 0.035753</t>
         </is>
       </c>
       <c r="R784" s="2" t="n">
@@ -55762,11 +55762,11 @@
         <v>0.12425533895995729</v>
       </c>
       <c r="P785" t="n">
-        <v>0.0</v>
+        <v>0.04804634291979708</v>
       </c>
       <c r="Q785" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.124255 ± 0</t>
+          <t xml:space="preserve">0.124255 ± 0.0480463</t>
         </is>
       </c>
       <c r="R785" t="n">
@@ -55833,11 +55833,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P786" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q786" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R786" s="2" t="n">
@@ -55904,11 +55904,11 @@
         <v>0.6634684347878455</v>
       </c>
       <c r="P787" t="n">
-        <v>0.0</v>
+        <v>0.030776966697295335</v>
       </c>
       <c r="Q787" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.663468 ± 0</t>
+          <t xml:space="preserve">0.663468 ± 0.030777</t>
         </is>
       </c>
       <c r="R787" t="n">
@@ -55975,11 +55975,11 @@
         <v>0.06398909685274679</v>
       </c>
       <c r="P788" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07851162174128527</v>
       </c>
       <c r="Q788" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0639891 ± 0</t>
+          <t xml:space="preserve">0.0639891 ± 0.0785116</t>
         </is>
       </c>
       <c r="R788" s="2" t="n">
@@ -56046,11 +56046,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P789" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q789" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R789" t="n">
@@ -56117,11 +56117,11 @@
         <v>0.7272377797305773</v>
       </c>
       <c r="P790" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06853438035938661</v>
       </c>
       <c r="Q790" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.727238 ± 0</t>
+          <t xml:space="preserve">0.727238 ± 0.0685344</t>
         </is>
       </c>
       <c r="R790" s="2" t="n">
@@ -56188,11 +56188,11 @@
         <v>0.08808312128922824</v>
       </c>
       <c r="P791" t="n">
-        <v>0.0</v>
+        <v>0.12211133981532986</v>
       </c>
       <c r="Q791" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0880831 ± 0</t>
+          <t xml:space="preserve">0.0880831 ± 0.122111</t>
         </is>
       </c>
       <c r="R791" t="n">
@@ -56259,11 +56259,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P792" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q792" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R792" s="2" t="n">
@@ -56330,11 +56330,11 @@
         <v>0.7219142973042739</v>
       </c>
       <c r="P793" t="n">
-        <v>0.0</v>
+        <v>0.10383327863741763</v>
       </c>
       <c r="Q793" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.721914 ± 0</t>
+          <t xml:space="preserve">0.721914 ± 0.103833</t>
         </is>
       </c>
       <c r="R793" t="n">
@@ -56401,11 +56401,11 @@
         <v>0.08416666666666661</v>
       </c>
       <c r="P794" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05145944726329341</v>
       </c>
       <c r="Q794" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0841667 ± 0</t>
+          <t xml:space="preserve">0.0841667 ± 0.0514594</t>
         </is>
       </c>
       <c r="R794" s="2" t="n">
@@ -56472,11 +56472,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P795" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q795" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R795" t="n">
@@ -56543,11 +56543,11 @@
         <v>0.709</v>
       </c>
       <c r="P796" s="2" t="n">
-        <v>0.0</v>
+        <v>0.035752983960348886</v>
       </c>
       <c r="Q796" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.709 ± 0</t>
+          <t xml:space="preserve">0.709 ± 0.035753</t>
         </is>
       </c>
       <c r="R796" s="2" t="n">
@@ -56685,11 +56685,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P798" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q798" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R798" s="2" t="n">
@@ -56898,11 +56898,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P801" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q801" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R801" t="n">
@@ -57111,11 +57111,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P804" s="2" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q804" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R804" s="2" t="n">
@@ -57324,11 +57324,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P807" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q807" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R807" t="n">
@@ -57537,11 +57537,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P810" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q810" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R810" s="2" t="n">
@@ -57750,11 +57750,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P813" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q813" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R813" t="n">
@@ -57963,11 +57963,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P816" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q816" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R816" s="2" t="n">
@@ -58176,11 +58176,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P819" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q819" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R819" t="n">
@@ -58389,11 +58389,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P822" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q822" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R822" s="2" t="n">
@@ -58602,11 +58602,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P825" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q825" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R825" t="n">
@@ -58815,11 +58815,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P828" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q828" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R828" s="2" t="n">
@@ -59028,11 +59028,11 @@
         <v>0.7877237737478027</v>
       </c>
       <c r="P831" t="n">
-        <v>0.0</v>
+        <v>0.03689484230729695</v>
       </c>
       <c r="Q831" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.787724 ± 0</t>
+          <t xml:space="preserve">0.787724 ± 0.0368948</t>
         </is>
       </c>
       <c r="R831" t="n">
@@ -59241,11 +59241,11 @@
         <v>0.791226876583324</v>
       </c>
       <c r="P834" s="2" t="n">
-        <v>0.0</v>
+        <v>0.038302917084754536</v>
       </c>
       <c r="Q834" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.791227 ± 0</t>
+          <t xml:space="preserve">0.791227 ± 0.0383029</t>
         </is>
       </c>
       <c r="R834" s="2" t="n">
@@ -59454,11 +59454,11 @@
         <v>0.8099974185935024</v>
       </c>
       <c r="P837" t="n">
-        <v>0.0</v>
+        <v>0.06426374995982846</v>
       </c>
       <c r="Q837" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.809997 ± 0</t>
+          <t xml:space="preserve">0.809997 ± 0.0642637</t>
         </is>
       </c>
       <c r="R837" t="n">
@@ -59667,11 +59667,11 @@
         <v>0.7931666666666668</v>
       </c>
       <c r="P840" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03701079370365774</v>
       </c>
       <c r="Q840" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.793167 ± 0</t>
+          <t xml:space="preserve">0.793167 ± 0.0370108</t>
         </is>
       </c>
       <c r="R840" s="2" t="n">
@@ -59880,11 +59880,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P843" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q843" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R843" t="n">
@@ -60093,11 +60093,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P846" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q846" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R846" s="2" t="n">
@@ -60306,11 +60306,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P849" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q849" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R849" t="n">
@@ -60519,11 +60519,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P852" s="2" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q852" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R852" s="2" t="n">
@@ -60732,11 +60732,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P855" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q855" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R855" t="n">
@@ -60945,11 +60945,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P858" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q858" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R858" s="2" t="n">
@@ -61158,11 +61158,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P861" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q861" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R861" t="n">
@@ -61371,11 +61371,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P864" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q864" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R864" s="2" t="n">
@@ -61584,11 +61584,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P867" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q867" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R867" t="n">
@@ -61797,11 +61797,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P870" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q870" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R870" s="2" t="n">
@@ -62010,11 +62010,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P873" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q873" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R873" t="n">
@@ -62223,11 +62223,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P876" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q876" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R876" s="2" t="n">
@@ -62436,11 +62436,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P879" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q879" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R879" t="n">
@@ -62649,11 +62649,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P882" s="2" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q882" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R882" s="2" t="n">
@@ -62862,11 +62862,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P885" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q885" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R885" t="n">
@@ -63075,11 +63075,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P888" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q888" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R888" s="2" t="n">
@@ -63288,11 +63288,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P891" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q891" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R891" t="n">
@@ -63501,11 +63501,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P894" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q894" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R894" s="2" t="n">
@@ -63714,11 +63714,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P897" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q897" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R897" t="n">
@@ -63927,11 +63927,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P900" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q900" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R900" s="2" t="n">
@@ -64069,11 +64069,11 @@
         <v>0.31723333333333337</v>
       </c>
       <c r="P902" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16810674290906433</v>
       </c>
       <c r="Q902" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.317233 ± 0</t>
+          <t xml:space="preserve">0.317233 ± 0.168107</t>
         </is>
       </c>
       <c r="R902" s="2" t="n">
@@ -64140,11 +64140,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P903" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q903" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R903" t="n">
@@ -64211,11 +64211,11 @@
         <v>0.5616333333333332</v>
       </c>
       <c r="P904" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03000974937368293</v>
       </c>
       <c r="Q904" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.561633 ± 0</t>
+          <t xml:space="preserve">0.561633 ± 0.0300097</t>
         </is>
       </c>
       <c r="R904" s="2" t="n">
@@ -64282,11 +64282,11 @@
         <v>0.3211784912479377</v>
       </c>
       <c r="P905" t="n">
-        <v>0.0</v>
+        <v>0.1701475701968604</v>
       </c>
       <c r="Q905" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.321178 ± 0</t>
+          <t xml:space="preserve">0.321178 ± 0.170148</t>
         </is>
       </c>
       <c r="R905" t="n">
@@ -64353,11 +64353,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P906" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q906" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R906" s="2" t="n">
@@ -64424,11 +64424,11 @@
         <v>0.5557611890777181</v>
       </c>
       <c r="P907" t="n">
-        <v>0.0</v>
+        <v>0.025820241232995436</v>
       </c>
       <c r="Q907" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.555761 ± 0</t>
+          <t xml:space="preserve">0.555761 ± 0.0258202</t>
         </is>
       </c>
       <c r="R907" t="n">
@@ -64495,11 +64495,11 @@
         <v>0.3200597875159373</v>
       </c>
       <c r="P908" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16854748843615802</v>
       </c>
       <c r="Q908" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.32006 ± 0</t>
+          <t xml:space="preserve">0.32006 ± 0.168547</t>
         </is>
       </c>
       <c r="R908" s="2" t="n">
@@ -64566,11 +64566,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P909" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q909" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R909" t="n">
@@ -64637,11 +64637,11 @@
         <v>0.5581734773700279</v>
       </c>
       <c r="P910" s="2" t="n">
-        <v>0.0</v>
+        <v>0.027233001135501755</v>
       </c>
       <c r="Q910" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.558173 ± 0</t>
+          <t xml:space="preserve">0.558173 ± 0.027233</t>
         </is>
       </c>
       <c r="R910" s="2" t="n">
@@ -64708,11 +64708,11 @@
         <v>0.3381175078853728</v>
       </c>
       <c r="P911" t="n">
-        <v>0.0</v>
+        <v>0.13555225169206808</v>
       </c>
       <c r="Q911" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.338118 ± 0</t>
+          <t xml:space="preserve">0.338118 ± 0.135552</t>
         </is>
       </c>
       <c r="R911" t="n">
@@ -64779,11 +64779,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P912" s="2" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q912" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R912" s="2" t="n">
@@ -64850,11 +64850,11 @@
         <v>0.5647989011003817</v>
       </c>
       <c r="P913" t="n">
-        <v>0.0</v>
+        <v>0.035259229369685424</v>
       </c>
       <c r="Q913" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.564799 ± 0</t>
+          <t xml:space="preserve">0.564799 ± 0.0352592</t>
         </is>
       </c>
       <c r="R913" t="n">
@@ -64921,11 +64921,11 @@
         <v>0.31723333333333337</v>
       </c>
       <c r="P914" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16810674290906433</v>
       </c>
       <c r="Q914" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.317233 ± 0</t>
+          <t xml:space="preserve">0.317233 ± 0.168107</t>
         </is>
       </c>
       <c r="R914" s="2" t="n">
@@ -64992,11 +64992,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P915" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q915" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R915" t="n">
@@ -65063,11 +65063,11 @@
         <v>0.5616333333333332</v>
       </c>
       <c r="P916" s="2" t="n">
-        <v>0.0</v>
+        <v>0.03000974937368293</v>
       </c>
       <c r="Q916" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.561633 ± 0</t>
+          <t xml:space="preserve">0.561633 ± 0.0300097</t>
         </is>
       </c>
       <c r="R916" s="2" t="n">
@@ -65205,11 +65205,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P918" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q918" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R918" s="2" t="n">
@@ -65418,11 +65418,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P921" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q921" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R921" t="n">
@@ -65631,11 +65631,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P924" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q924" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R924" s="2" t="n">
@@ -65844,11 +65844,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P927" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q927" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R927" t="n">
@@ -66057,11 +66057,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P930" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q930" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R930" s="2" t="n">
@@ -66270,11 +66270,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P933" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q933" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R933" t="n">
@@ -66483,11 +66483,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P936" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q936" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R936" s="2" t="n">
@@ -66696,11 +66696,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P939" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q939" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R939" t="n">
@@ -66909,11 +66909,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P942" s="2" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q942" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R942" s="2" t="n">
@@ -67122,11 +67122,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P945" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q945" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R945" t="n">
@@ -67335,11 +67335,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P948" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q948" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R948" s="2" t="n">
@@ -67548,11 +67548,11 @@
         <v>0.8769396803256558</v>
       </c>
       <c r="P951" t="n">
-        <v>0.0</v>
+        <v>0.16817702217177427</v>
       </c>
       <c r="Q951" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.87694 ± 0</t>
+          <t xml:space="preserve">0.87694 ± 0.168177</t>
         </is>
       </c>
       <c r="R951" t="n">
@@ -67761,11 +67761,11 @@
         <v>0.8782332648859651</v>
       </c>
       <c r="P954" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16633285756966534</v>
       </c>
       <c r="Q954" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878233 ± 0</t>
+          <t xml:space="preserve">0.878233 ± 0.166333</t>
         </is>
       </c>
       <c r="R954" s="2" t="n">
@@ -67974,11 +67974,11 @@
         <v>0.9029164089857545</v>
       </c>
       <c r="P957" t="n">
-        <v>0.0</v>
+        <v>0.13088620891081568</v>
       </c>
       <c r="Q957" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.902916 ± 0</t>
+          <t xml:space="preserve">0.902916 ± 0.130886</t>
         </is>
       </c>
       <c r="R957" t="n">
@@ -68187,11 +68187,11 @@
         <v>0.8788666666666668</v>
       </c>
       <c r="P960" s="2" t="n">
-        <v>0.0</v>
+        <v>0.16540644471731744</v>
       </c>
       <c r="Q960" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.878867 ± 0</t>
+          <t xml:space="preserve">0.878867 ± 0.165406</t>
         </is>
       </c>
       <c r="R960" s="2" t="n">
@@ -68400,11 +68400,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P963" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q963" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R963" t="n">
@@ -68613,11 +68613,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P966" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q966" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R966" s="2" t="n">
@@ -68826,11 +68826,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P969" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q969" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R969" t="n">
@@ -69037,11 +69037,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P972" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q972" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R972" s="2" t="n">
@@ -69248,11 +69248,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P975" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q975" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R975" t="n">
@@ -69461,11 +69461,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P978" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q978" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R978" s="2" t="n">
@@ -69674,11 +69674,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P981" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q981" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R981" t="n">
@@ -69887,11 +69887,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P984" s="2" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q984" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R984" s="2" t="n">
@@ -70100,11 +70100,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P987" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q987" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R987" t="n">
@@ -70313,11 +70313,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P990" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q990" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R990" s="2" t="n">
@@ -70526,11 +70526,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P993" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q993" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R993" t="n">
@@ -70739,11 +70739,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P996" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q996" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R996" s="2" t="n">
@@ -70952,11 +70952,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P999" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q999" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R999" t="n">
@@ -71165,11 +71165,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P1002" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q1002" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R1002" s="2" t="n">
@@ -71378,11 +71378,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1005" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1005" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1005" t="n">
@@ -71591,11 +71591,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1008" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1008" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1008" s="2" t="n">
@@ -71804,11 +71804,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P1011" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R1011" t="n">
@@ -72017,11 +72017,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P1014" s="2" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q1014" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R1014" s="2" t="n">
@@ -72222,11 +72222,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P1017" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R1017" t="n">
@@ -72427,11 +72427,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1020" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1020" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1020" s="2" t="n">
@@ -72569,11 +72569,11 @@
         <v>0.21159863945578242</v>
       </c>
       <c r="P1022" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07640880916269864</v>
       </c>
       <c r="Q1022" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.211599 ± 0</t>
+          <t xml:space="preserve">0.211599 ± 0.0764088</t>
         </is>
       </c>
       <c r="R1022" s="2" t="n">
@@ -72640,11 +72640,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1023" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1023" t="n">
@@ -72711,11 +72711,11 @@
         <v>0.3883673469387755</v>
       </c>
       <c r="P1024" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0600440985549243</v>
       </c>
       <c r="Q1024" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.388367 ± 0</t>
+          <t xml:space="preserve">0.388367 ± 0.0600441</t>
         </is>
       </c>
       <c r="R1024" s="2" t="n">
@@ -72782,11 +72782,11 @@
         <v>0.2681541240261808</v>
       </c>
       <c r="P1025" t="n">
-        <v>0.0</v>
+        <v>0.06015043923079675</v>
       </c>
       <c r="Q1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.268154 ± 0</t>
+          <t xml:space="preserve">0.268154 ± 0.0601504</t>
         </is>
       </c>
       <c r="R1025" t="n">
@@ -72853,11 +72853,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P1026" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q1026" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R1026" s="2" t="n">
@@ -72924,11 +72924,11 @@
         <v>0.31738889320823727</v>
       </c>
       <c r="P1027" t="n">
-        <v>0.0</v>
+        <v>0.020416649622090235</v>
       </c>
       <c r="Q1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.317389 ± 0</t>
+          <t xml:space="preserve">0.317389 ± 0.0204166</t>
         </is>
       </c>
       <c r="R1027" t="n">
@@ -72995,11 +72995,11 @@
         <v>0.27590788136877864</v>
       </c>
       <c r="P1028" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06925141152347221</v>
       </c>
       <c r="Q1028" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.275908 ± 0</t>
+          <t xml:space="preserve">0.275908 ± 0.0692514</t>
         </is>
       </c>
       <c r="R1028" s="2" t="n">
@@ -73066,11 +73066,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P1029" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R1029" t="n">
@@ -73137,11 +73137,11 @@
         <v>0.32108390348674426</v>
       </c>
       <c r="P1030" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0389354681152862</v>
       </c>
       <c r="Q1030" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.321084 ± 0</t>
+          <t xml:space="preserve">0.321084 ± 0.0389355</t>
         </is>
       </c>
       <c r="R1030" s="2" t="n">
@@ -73208,11 +73208,11 @@
         <v>0.24335129223948151</v>
       </c>
       <c r="P1031" t="n">
-        <v>0.0</v>
+        <v>0.07009671735466518</v>
       </c>
       <c r="Q1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.243351 ± 0</t>
+          <t xml:space="preserve">0.243351 ± 0.0700967</t>
         </is>
       </c>
       <c r="R1031" t="n">
@@ -73279,11 +73279,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P1032" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q1032" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R1032" s="2" t="n">
@@ -73350,11 +73350,11 @@
         <v>0.5051839516711457</v>
       </c>
       <c r="P1033" t="n">
-        <v>0.0</v>
+        <v>0.01617503424021354</v>
       </c>
       <c r="Q1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.505184 ± 0</t>
+          <t xml:space="preserve">0.505184 ± 0.016175</t>
         </is>
       </c>
       <c r="R1033" t="n">
@@ -73421,11 +73421,11 @@
         <v>0.21159863945578242</v>
       </c>
       <c r="P1034" s="2" t="n">
-        <v>0.0</v>
+        <v>0.07640880916269864</v>
       </c>
       <c r="Q1034" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.211599 ± 0</t>
+          <t xml:space="preserve">0.211599 ± 0.0764088</t>
         </is>
       </c>
       <c r="R1034" s="2" t="n">
@@ -73492,11 +73492,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1035" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1035" t="n">
@@ -73563,11 +73563,11 @@
         <v>0.3883673469387755</v>
       </c>
       <c r="P1036" s="2" t="n">
-        <v>0.0</v>
+        <v>0.0600440985549243</v>
       </c>
       <c r="Q1036" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.388367 ± 0</t>
+          <t xml:space="preserve">0.388367 ± 0.0600441</t>
         </is>
       </c>
       <c r="R1036" s="2" t="n">
@@ -73705,11 +73705,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1038" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1038" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1038" s="2" t="n">
@@ -73918,11 +73918,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P1041" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q1041" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R1041" t="n">
@@ -74131,11 +74131,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P1044" s="2" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q1044" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R1044" s="2" t="n">
@@ -74250,7 +74250,9 @@
       <c r="M1046" s="2"/>
       <c r="N1046" s="2"/>
       <c r="O1046" s="2"/>
-      <c r="P1046" s="2"/>
+      <c r="P1046" s="2" t="n">
+        <v>0.06820497086890176</v>
+      </c>
       <c r="Q1046" s="2"/>
       <c r="R1046" s="2" t="n">
         <v>0</v>
@@ -74316,11 +74318,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P1047" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R1047" t="n">
@@ -74501,11 +74503,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1050" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1050" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1050" s="2" t="n">
@@ -74714,11 +74716,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1053" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1053" t="n">
@@ -74927,11 +74929,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P1056" s="2" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q1056" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R1056" s="2" t="n">
@@ -75140,11 +75142,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P1059" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q1059" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R1059" t="n">
@@ -75343,11 +75345,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P1062" s="2" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q1062" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R1062" s="2" t="n">
@@ -75546,11 +75548,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1065" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1065" t="n">
@@ -75759,11 +75761,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1068" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1068" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1068" s="2" t="n">
@@ -75972,11 +75974,11 @@
         <v>0.5855430172344179</v>
       </c>
       <c r="P1071" t="n">
-        <v>0.0</v>
+        <v>0.05657946410020667</v>
       </c>
       <c r="Q1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.585543 ± 0</t>
+          <t xml:space="preserve">0.585543 ± 0.0565795</t>
         </is>
       </c>
       <c r="R1071" t="n">
@@ -76185,11 +76187,11 @@
         <v>0.596991784855523</v>
       </c>
       <c r="P1074" s="2" t="n">
-        <v>0.0</v>
+        <v>0.057269427451624055</v>
       </c>
       <c r="Q1074" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.596992 ± 0</t>
+          <t xml:space="preserve">0.596992 ± 0.0572694</t>
         </is>
       </c>
       <c r="R1074" s="2" t="n">
@@ -76388,11 +76390,11 @@
         <v>0.7485352439106271</v>
       </c>
       <c r="P1077" t="n">
-        <v>0.0</v>
+        <v>0.06820497086890176</v>
       </c>
       <c r="Q1077" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.748535 ± 0</t>
+          <t xml:space="preserve">0.748535 ± 0.068205</t>
         </is>
       </c>
       <c r="R1077" t="n">
@@ -76591,11 +76593,11 @@
         <v>0.5999659863945579</v>
       </c>
       <c r="P1080" s="2" t="n">
-        <v>0.0</v>
+        <v>0.04725476003947366</v>
       </c>
       <c r="Q1080" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.599966 ± 0</t>
+          <t xml:space="preserve">0.599966 ± 0.0472548</t>
         </is>
       </c>
       <c r="R1080" s="2" t="n">
